--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/182.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/182.xlsx
@@ -426,13 +426,13 @@
         <v>-5.875393577905005</v>
       </c>
       <c r="E2">
-        <v>-18.32455366127784</v>
+        <v>-21.84917819329787</v>
       </c>
       <c r="F2">
-        <v>2.845422393210868</v>
+        <v>1.2291570678559</v>
       </c>
       <c r="G2">
-        <v>-15.31298913238692</v>
+        <v>-17.52598619847799</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-5.695777448746377</v>
       </c>
       <c r="E3">
-        <v>-19.12582638066904</v>
+        <v>-21.43463262568771</v>
       </c>
       <c r="F3">
-        <v>2.97180054155702</v>
+        <v>1.549930366204499</v>
       </c>
       <c r="G3">
-        <v>-14.94495744005891</v>
+        <v>-17.07857424520934</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-5.453973860081031</v>
       </c>
       <c r="E4">
-        <v>-19.68217658335539</v>
+        <v>-23.10928495609425</v>
       </c>
       <c r="F4">
-        <v>2.758806349283653</v>
+        <v>1.042986102672331</v>
       </c>
       <c r="G4">
-        <v>-14.46091595567099</v>
+        <v>-17.34721177353903</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-5.16627975632778</v>
       </c>
       <c r="E5">
-        <v>-18.70980453053238</v>
+        <v>-22.86581155107185</v>
       </c>
       <c r="F5">
-        <v>3.103903786787486</v>
+        <v>1.64698619952629</v>
       </c>
       <c r="G5">
-        <v>-14.16803530235721</v>
+        <v>-16.50810600370043</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-4.820390597910675</v>
       </c>
       <c r="E6">
-        <v>-20.16078194427806</v>
+        <v>-24.62304966195627</v>
       </c>
       <c r="F6">
-        <v>3.263653786183778</v>
+        <v>1.43655919454185</v>
       </c>
       <c r="G6">
-        <v>-13.41966496465895</v>
+        <v>-16.11075446480387</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-4.425494524183206</v>
       </c>
       <c r="E7">
-        <v>-20.90660802791934</v>
+        <v>-23.82532273771308</v>
       </c>
       <c r="F7">
-        <v>3.430498788081239</v>
+        <v>1.550563848570675</v>
       </c>
       <c r="G7">
-        <v>-13.15555957317251</v>
+        <v>-16.00219174493455</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-3.982275222574368</v>
       </c>
       <c r="E8">
-        <v>-21.99752194484114</v>
+        <v>-25.69916905429501</v>
       </c>
       <c r="F8">
-        <v>3.413155624601262</v>
+        <v>1.870561131020708</v>
       </c>
       <c r="G8">
-        <v>-12.57533680923215</v>
+        <v>-15.14718376959806</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-3.507625877228433</v>
       </c>
       <c r="E9">
-        <v>-22.21628799567769</v>
+        <v>-26.00889856252363</v>
       </c>
       <c r="F9">
-        <v>3.554064274721572</v>
+        <v>1.81995380849284</v>
       </c>
       <c r="G9">
-        <v>-11.72844629155795</v>
+        <v>-13.24712264169768</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-3.015938071237379</v>
       </c>
       <c r="E10">
-        <v>-23.58455736014727</v>
+        <v>-24.68202850743217</v>
       </c>
       <c r="F10">
-        <v>3.428028206853154</v>
+        <v>1.343058781000221</v>
       </c>
       <c r="G10">
-        <v>-11.05932544825154</v>
+        <v>-14.0199496345673</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-2.528796221885317</v>
       </c>
       <c r="E11">
-        <v>-22.71976826432448</v>
+        <v>-27.69878015101796</v>
       </c>
       <c r="F11">
-        <v>3.804997725905206</v>
+        <v>2.158298323973239</v>
       </c>
       <c r="G11">
-        <v>-10.50205800708048</v>
+        <v>-14.46675575800226</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-2.069700639199397</v>
       </c>
       <c r="E12">
-        <v>-23.8961842989851</v>
+        <v>-27.63613777006986</v>
       </c>
       <c r="F12">
-        <v>4.187278994597642</v>
+        <v>2.298527564255825</v>
       </c>
       <c r="G12">
-        <v>-10.61155099024633</v>
+        <v>-12.52908848804853</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-1.656390830091625</v>
       </c>
       <c r="E13">
-        <v>-25.34130186736485</v>
+        <v>-26.88471449255509</v>
       </c>
       <c r="F13">
-        <v>3.988717114331674</v>
+        <v>2.500155499174082</v>
       </c>
       <c r="G13">
-        <v>-9.37381415566024</v>
+        <v>-13.12170593448793</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-1.310683152959134</v>
       </c>
       <c r="E14">
-        <v>-25.97018463823206</v>
+        <v>-28.98007564369623</v>
       </c>
       <c r="F14">
-        <v>3.866309316715529</v>
+        <v>2.273484422614981</v>
       </c>
       <c r="G14">
-        <v>-8.599235884200342</v>
+        <v>-13.23573105449704</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-1.03837044438881</v>
       </c>
       <c r="E15">
-        <v>-26.66781417300971</v>
+        <v>-28.54985702754552</v>
       </c>
       <c r="F15">
-        <v>4.258474494026221</v>
+        <v>2.622385921727699</v>
       </c>
       <c r="G15">
-        <v>-8.418384091935495</v>
+        <v>-12.1263275177408</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-0.8415366030181767</v>
       </c>
       <c r="E16">
-        <v>-26.49973533174101</v>
+        <v>-30.34653361856275</v>
       </c>
       <c r="F16">
-        <v>4.904089631220183</v>
+        <v>2.71473656477472</v>
       </c>
       <c r="G16">
-        <v>-7.865662029789857</v>
+        <v>-11.29705241288106</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-0.7112171863815281</v>
       </c>
       <c r="E17">
-        <v>-28.93359085800749</v>
+        <v>-30.58520457690001</v>
       </c>
       <c r="F17">
-        <v>4.911118118072903</v>
+        <v>3.041401249128753</v>
       </c>
       <c r="G17">
-        <v>-8.363164192340452</v>
+        <v>-10.91761754644303</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-0.6389308325858111</v>
       </c>
       <c r="E18">
-        <v>-29.22205012382209</v>
+        <v>-30.75483894899034</v>
       </c>
       <c r="F18">
-        <v>4.68138098686151</v>
+        <v>3.246481662942668</v>
       </c>
       <c r="G18">
-        <v>-8.020214848290733</v>
+        <v>-10.65245609092957</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-0.6175808507352128</v>
       </c>
       <c r="E19">
-        <v>-31.03374539888575</v>
+        <v>-32.44316274242603</v>
       </c>
       <c r="F19">
-        <v>5.04647112784185</v>
+        <v>3.18421351375942</v>
       </c>
       <c r="G19">
-        <v>-7.432377829610044</v>
+        <v>-10.61358035466191</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-0.6427265014220803</v>
       </c>
       <c r="E20">
-        <v>-31.91579477338877</v>
+        <v>-33.76012449638871</v>
       </c>
       <c r="F20">
-        <v>5.231563589297004</v>
+        <v>3.467544836855199</v>
       </c>
       <c r="G20">
-        <v>-7.955076554260033</v>
+        <v>-11.21330223182858</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-0.7153582344222198</v>
       </c>
       <c r="E21">
-        <v>-32.04041384960585</v>
+        <v>-34.07215673365023</v>
       </c>
       <c r="F21">
-        <v>5.29682969377818</v>
+        <v>3.067741445914342</v>
       </c>
       <c r="G21">
-        <v>-7.541089524028632</v>
+        <v>-10.78457665285634</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-0.8353223616736952</v>
       </c>
       <c r="E22">
-        <v>-31.5338927106629</v>
+        <v>-35.41862602424689</v>
       </c>
       <c r="F22">
-        <v>5.235448419907578</v>
+        <v>3.787290310064678</v>
       </c>
       <c r="G22">
-        <v>-6.757665474887801</v>
+        <v>-9.697694757403758</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-1.003198068658523</v>
       </c>
       <c r="E23">
-        <v>-31.96621027451616</v>
+        <v>-35.36228048640645</v>
       </c>
       <c r="F23">
-        <v>5.306984416107977</v>
+        <v>3.240723308234131</v>
       </c>
       <c r="G23">
-        <v>-6.677116591371794</v>
+        <v>-10.62256848580103</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-1.214556582845471</v>
       </c>
       <c r="E24">
-        <v>-31.72287725218801</v>
+        <v>-35.65168846752565</v>
       </c>
       <c r="F24">
-        <v>5.578105366595718</v>
+        <v>3.78245208849301</v>
       </c>
       <c r="G24">
-        <v>-6.182676683445025</v>
+        <v>-9.356546350127401</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-1.465768141047708</v>
       </c>
       <c r="E25">
-        <v>-32.62948227699762</v>
+        <v>-35.46965060512832</v>
       </c>
       <c r="F25">
-        <v>5.355369799236484</v>
+        <v>3.535169079444464</v>
       </c>
       <c r="G25">
-        <v>-6.432662598206471</v>
+        <v>-9.492950757981992</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-1.74630883464947</v>
       </c>
       <c r="E26">
-        <v>-32.68904529562051</v>
+        <v>-37.6610991820012</v>
       </c>
       <c r="F26">
-        <v>5.726630058463376</v>
+        <v>3.110832500167533</v>
       </c>
       <c r="G26">
-        <v>-6.015259084978542</v>
+        <v>-9.007508912830961</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-2.050651423873786</v>
       </c>
       <c r="E27">
-        <v>-33.16345502537506</v>
+        <v>-36.16314337889995</v>
       </c>
       <c r="F27">
-        <v>5.078243435917397</v>
+        <v>3.603688115875952</v>
       </c>
       <c r="G27">
-        <v>-6.029643405346675</v>
+        <v>-10.07691443838173</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-2.368881326910061</v>
       </c>
       <c r="E28">
-        <v>-32.71908492795039</v>
+        <v>-37.26397465389855</v>
       </c>
       <c r="F28">
-        <v>4.883384260081727</v>
+        <v>2.819142377250065</v>
       </c>
       <c r="G28">
-        <v>-5.487554815473175</v>
+        <v>-9.186867649057595</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-2.695304595460909</v>
       </c>
       <c r="E29">
-        <v>-33.78399861135715</v>
+        <v>-34.82268110907447</v>
       </c>
       <c r="F29">
-        <v>5.050243515332427</v>
+        <v>3.126557116201932</v>
       </c>
       <c r="G29">
-        <v>-5.509669259675507</v>
+        <v>-10.09614539741936</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-3.025577069686559</v>
       </c>
       <c r="E30">
-        <v>-30.56822279937125</v>
+        <v>-35.50704674348366</v>
       </c>
       <c r="F30">
-        <v>5.155461768942393</v>
+        <v>3.108021422167628</v>
       </c>
       <c r="G30">
-        <v>-6.515846675971738</v>
+        <v>-8.216990364599473</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-3.354336144952398</v>
       </c>
       <c r="E31">
-        <v>-32.3659816956763</v>
+        <v>-35.74681585676777</v>
       </c>
       <c r="F31">
-        <v>4.783137259340325</v>
+        <v>3.269429561657386</v>
       </c>
       <c r="G31">
-        <v>-6.744741105102487</v>
+        <v>-9.133018315315811</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-3.683132777598405</v>
       </c>
       <c r="E32">
-        <v>-32.14734697058597</v>
+        <v>-35.31482887151707</v>
       </c>
       <c r="F32">
-        <v>4.991316985630756</v>
+        <v>2.899928799702547</v>
       </c>
       <c r="G32">
-        <v>-5.769854965243447</v>
+        <v>-8.43049737806369</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-4.005529454902411</v>
       </c>
       <c r="E33">
-        <v>-32.48584813842233</v>
+        <v>-35.26869051408993</v>
       </c>
       <c r="F33">
-        <v>4.980370410343239</v>
+        <v>2.832470846234404</v>
       </c>
       <c r="G33">
-        <v>-6.412713250786823</v>
+        <v>-9.172430359960833</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-4.322371583819216</v>
       </c>
       <c r="E34">
-        <v>-30.7134305826642</v>
+        <v>-33.56863797297436</v>
       </c>
       <c r="F34">
-        <v>5.163478488286348</v>
+        <v>2.382646103954391</v>
       </c>
       <c r="G34">
-        <v>-6.470962299550299</v>
+        <v>-8.801996866844084</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-4.627482489775616</v>
       </c>
       <c r="E35">
-        <v>-30.00780829126301</v>
+        <v>-35.24039660849</v>
       </c>
       <c r="F35">
-        <v>4.710321628760251</v>
+        <v>3.139606852945153</v>
       </c>
       <c r="G35">
-        <v>-6.062632991645512</v>
+        <v>-9.900478913866275</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-4.916962890489889</v>
       </c>
       <c r="E36">
-        <v>-29.25310187009269</v>
+        <v>-34.66729558044928</v>
       </c>
       <c r="F36">
-        <v>4.734520655148165</v>
+        <v>3.429684763240704</v>
       </c>
       <c r="G36">
-        <v>-6.19159860367336</v>
+        <v>-8.766302564839663</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-5.187819965600299</v>
       </c>
       <c r="E37">
-        <v>-30.59559742474761</v>
+        <v>-32.45199553097799</v>
       </c>
       <c r="F37">
-        <v>4.781811697489102</v>
+        <v>3.079723764870557</v>
       </c>
       <c r="G37">
-        <v>-6.2769047411293</v>
+        <v>-10.40646600463402</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-5.433008788857109</v>
       </c>
       <c r="E38">
-        <v>-29.25077876292675</v>
+        <v>-32.49838748294957</v>
       </c>
       <c r="F38">
-        <v>5.210234238027867</v>
+        <v>2.992243017513512</v>
       </c>
       <c r="G38">
-        <v>-5.893434319678901</v>
+        <v>-9.758161871678546</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-5.65210372838874</v>
       </c>
       <c r="E39">
-        <v>-29.29838208169538</v>
+        <v>-33.32448529685082</v>
       </c>
       <c r="F39">
-        <v>4.645270908283575</v>
+        <v>3.357710080501727</v>
       </c>
       <c r="G39">
-        <v>-6.365564461216522</v>
+        <v>-9.79421040205567</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-5.837740958313567</v>
       </c>
       <c r="E40">
-        <v>-27.53103641682584</v>
+        <v>-30.91919538462473</v>
       </c>
       <c r="F40">
-        <v>4.89588128346046</v>
+        <v>3.297402559241793</v>
       </c>
       <c r="G40">
-        <v>-6.432116358192491</v>
+        <v>-9.342267967216523</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-5.990520325269173</v>
       </c>
       <c r="E41">
-        <v>-28.90982995488925</v>
+        <v>-32.71395190266269</v>
       </c>
       <c r="F41">
-        <v>4.970576772962161</v>
+        <v>2.85354046973341</v>
       </c>
       <c r="G41">
-        <v>-6.992065341250359</v>
+        <v>-10.63932315677528</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-6.109754548521176</v>
       </c>
       <c r="E42">
-        <v>-27.36302550266726</v>
+        <v>-30.05777094498964</v>
       </c>
       <c r="F42">
-        <v>4.415194864006279</v>
+        <v>2.720841751078739</v>
       </c>
       <c r="G42">
-        <v>-6.183014359090031</v>
+        <v>-11.34850822219795</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-6.196031054719053</v>
       </c>
       <c r="E43">
-        <v>-26.46251127539796</v>
+        <v>-31.26631650273468</v>
       </c>
       <c r="F43">
-        <v>4.928529380907244</v>
+        <v>3.089167403244322</v>
       </c>
       <c r="G43">
-        <v>-7.04493144296698</v>
+        <v>-9.433112647359664</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-6.255223908839426</v>
       </c>
       <c r="E44">
-        <v>-26.32965037648692</v>
+        <v>-31.21714633195939</v>
       </c>
       <c r="F44">
-        <v>4.950729770429874</v>
+        <v>3.123766626378928</v>
       </c>
       <c r="G44">
-        <v>-7.268982543973776</v>
+        <v>-10.53141923546827</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-6.289723922132159</v>
       </c>
       <c r="E45">
-        <v>-23.76752129547917</v>
+        <v>-29.99348019950274</v>
       </c>
       <c r="F45">
-        <v>4.830933503868287</v>
+        <v>2.735852115745274</v>
       </c>
       <c r="G45">
-        <v>-7.106795607459341</v>
+        <v>-9.26796939367866</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-6.308681021953616</v>
       </c>
       <c r="E46">
-        <v>-24.82512828607456</v>
+        <v>-30.70376229065782</v>
       </c>
       <c r="F46">
-        <v>4.876848305768708</v>
+        <v>3.358166187805374</v>
       </c>
       <c r="G46">
-        <v>-6.841177296661456</v>
+        <v>-8.749048001488982</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-6.316599818578156</v>
       </c>
       <c r="E47">
-        <v>-24.70740607577116</v>
+        <v>-28.62719430664852</v>
       </c>
       <c r="F47">
-        <v>5.139152765425198</v>
+        <v>3.101550399797143</v>
       </c>
       <c r="G47">
-        <v>-7.729519155032869</v>
+        <v>-10.20387717035832</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-6.32095038877302</v>
       </c>
       <c r="E48">
-        <v>-25.35878177703446</v>
+        <v>-28.07025540234117</v>
       </c>
       <c r="F48">
-        <v>4.950139048123416</v>
+        <v>3.30146318120898</v>
       </c>
       <c r="G48">
-        <v>-8.149726700332561</v>
+        <v>-11.02402179062075</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-6.328163731741057</v>
       </c>
       <c r="E49">
-        <v>-23.80110445872006</v>
+        <v>-27.09386659307336</v>
       </c>
       <c r="F49">
-        <v>5.246890695146628</v>
+        <v>3.195478413935941</v>
       </c>
       <c r="G49">
-        <v>-7.802361088533453</v>
+        <v>-10.59388260870324</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-6.339806561482498</v>
       </c>
       <c r="E50">
-        <v>-23.8766982753301</v>
+        <v>-25.77535157252605</v>
       </c>
       <c r="F50">
-        <v>5.031151940521805</v>
+        <v>2.726375219547284</v>
       </c>
       <c r="G50">
-        <v>-7.90630559737549</v>
+        <v>-12.13925188752611</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-6.361704562503095</v>
       </c>
       <c r="E51">
-        <v>-23.30730153902765</v>
+        <v>-26.37669216447861</v>
       </c>
       <c r="F51">
-        <v>4.711550584550632</v>
+        <v>2.923489592606539</v>
       </c>
       <c r="G51">
-        <v>-7.850565942130781</v>
+        <v>-11.07126327546615</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-6.392694916630099</v>
       </c>
       <c r="E52">
-        <v>-21.19713227788143</v>
+        <v>-24.04339593202645</v>
       </c>
       <c r="F52">
-        <v>4.99174300252201</v>
+        <v>2.908379454467332</v>
       </c>
       <c r="G52">
-        <v>-7.558099107009407</v>
+        <v>-11.62433956598449</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-6.435395228085554</v>
       </c>
       <c r="E53">
-        <v>-21.80883854683755</v>
+        <v>-25.87135069301465</v>
       </c>
       <c r="F53">
-        <v>4.80378403335991</v>
+        <v>3.280132246233926</v>
       </c>
       <c r="G53">
-        <v>-7.517276769964654</v>
+        <v>-10.80496630283271</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-6.488937728524953</v>
       </c>
       <c r="E54">
-        <v>-22.42547632398801</v>
+        <v>-25.17424193274789</v>
       </c>
       <c r="F54">
-        <v>4.962129285609207</v>
+        <v>2.548268484885133</v>
       </c>
       <c r="G54">
-        <v>-8.238935970979302</v>
+        <v>-11.29692992269611</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-6.553967528240319</v>
       </c>
       <c r="E55">
-        <v>-20.81335316267938</v>
+        <v>-23.57058701783361</v>
       </c>
       <c r="F55">
-        <v>4.800789245473814</v>
+        <v>2.943553562849242</v>
       </c>
       <c r="G55">
-        <v>-8.01214704881153</v>
+        <v>-10.12771807022739</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-6.633106803231422</v>
       </c>
       <c r="E56">
-        <v>-20.41178620157521</v>
+        <v>-22.98124235352737</v>
       </c>
       <c r="F56">
-        <v>4.903487822972315</v>
+        <v>3.079910642168578</v>
       </c>
       <c r="G56">
-        <v>-8.964600932096467</v>
+        <v>-11.39698122998396</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-6.724215936055359</v>
       </c>
       <c r="E57">
-        <v>-19.63944137414501</v>
+        <v>-21.1839453615711</v>
       </c>
       <c r="F57">
-        <v>5.045031539164716</v>
+        <v>2.973278139176125</v>
       </c>
       <c r="G57">
-        <v>-8.043828969622353</v>
+        <v>-11.45552491730043</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-6.83213803091968</v>
       </c>
       <c r="E58">
-        <v>-19.32125267647006</v>
+        <v>-24.60224132389103</v>
       </c>
       <c r="F58">
-        <v>4.979402766028906</v>
+        <v>2.885371374927828</v>
       </c>
       <c r="G58">
-        <v>-7.773559342341794</v>
+        <v>-10.84860260358585</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-6.954091361108605</v>
       </c>
       <c r="E59">
-        <v>-20.65286404384755</v>
+        <v>-21.10369174520716</v>
       </c>
       <c r="F59">
-        <v>4.96444783106941</v>
+        <v>3.673786107105132</v>
       </c>
       <c r="G59">
-        <v>-8.637816981915009</v>
+        <v>-13.31984870610438</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-7.092222411788454</v>
       </c>
       <c r="E60">
-        <v>-20.31187900801799</v>
+        <v>-22.520519936461</v>
       </c>
       <c r="F60">
-        <v>4.678626922274561</v>
+        <v>3.298734455916678</v>
       </c>
       <c r="G60">
-        <v>-9.260202853843531</v>
+        <v>-11.13474298618167</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-7.244933949915773</v>
       </c>
       <c r="E61">
-        <v>-18.75733539371689</v>
+        <v>-22.41929948544155</v>
       </c>
       <c r="F61">
-        <v>4.82522741145496</v>
+        <v>3.270330690323271</v>
       </c>
       <c r="G61">
-        <v>-9.210640676575101</v>
+        <v>-12.51979909726533</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-7.41099129476631</v>
       </c>
       <c r="E62">
-        <v>-18.67392543096961</v>
+        <v>-20.36852568937993</v>
       </c>
       <c r="F62">
-        <v>4.769504718820222</v>
+        <v>3.027852645022168</v>
       </c>
       <c r="G62">
-        <v>-9.432420743341957</v>
+        <v>-10.88892504825417</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-7.591446781137251</v>
       </c>
       <c r="E63">
-        <v>-17.80686756966898</v>
+        <v>-21.63325602413814</v>
       </c>
       <c r="F63">
-        <v>4.438616290789713</v>
+        <v>3.480651587011376</v>
       </c>
       <c r="G63">
-        <v>-8.512055977969174</v>
+        <v>-11.65297909544472</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-7.78183371562412</v>
       </c>
       <c r="E64">
-        <v>-17.03520654181394</v>
+        <v>-21.92221342209358</v>
       </c>
       <c r="F64">
-        <v>4.98349189470257</v>
+        <v>3.031471413038947</v>
       </c>
       <c r="G64">
-        <v>-10.04724201871324</v>
+        <v>-12.46323842672689</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-7.985216186558642</v>
       </c>
       <c r="E65">
-        <v>-17.72613393506023</v>
+        <v>-21.59472323880687</v>
       </c>
       <c r="F65">
-        <v>4.835093899308148</v>
+        <v>3.135748945335142</v>
       </c>
       <c r="G65">
-        <v>-10.00951504174771</v>
+        <v>-12.05225075075406</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-8.196070905579104</v>
       </c>
       <c r="E66">
-        <v>-17.52859737037165</v>
+        <v>-21.71542518500732</v>
       </c>
       <c r="F66">
-        <v>4.759688909556329</v>
+        <v>2.281518562724005</v>
       </c>
       <c r="G66">
-        <v>-9.416973737855718</v>
+        <v>-12.44429217460564</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-8.414791667179506</v>
       </c>
       <c r="E67">
-        <v>-17.92583058185048</v>
+        <v>-21.46480584800082</v>
       </c>
       <c r="F67">
-        <v>4.689939333628545</v>
+        <v>2.529602926965764</v>
       </c>
       <c r="G67">
-        <v>-9.269015526069071</v>
+        <v>-13.68918475337487</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-8.637713714239993</v>
       </c>
       <c r="E68">
-        <v>-17.2803690676412</v>
+        <v>-20.3758844596424</v>
       </c>
       <c r="F68">
-        <v>4.696562391766912</v>
+        <v>2.692246357069564</v>
       </c>
       <c r="G68">
-        <v>-9.442064362497854</v>
+        <v>-11.85810049705797</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-8.860110004600271</v>
       </c>
       <c r="E69">
-        <v>-17.02064749787928</v>
+        <v>-20.63713665361891</v>
       </c>
       <c r="F69">
-        <v>4.375730496299443</v>
+        <v>2.965712776018071</v>
       </c>
       <c r="G69">
-        <v>-10.29767485712249</v>
+        <v>-14.68086363548186</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-9.079446185368123</v>
       </c>
       <c r="E70">
-        <v>-16.86843190105945</v>
+        <v>-20.80843976838106</v>
       </c>
       <c r="F70">
-        <v>4.326572264684202</v>
+        <v>2.287948408740689</v>
       </c>
       <c r="G70">
-        <v>-10.67409712711978</v>
+        <v>-12.03131155021817</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-9.285757055101504</v>
       </c>
       <c r="E71">
-        <v>-17.35094986352475</v>
+        <v>-22.09467129772769</v>
       </c>
       <c r="F71">
-        <v>4.361257007938242</v>
+        <v>2.929053151487478</v>
       </c>
       <c r="G71">
-        <v>-9.398179770829275</v>
+        <v>-12.23422812850226</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-9.475540964810694</v>
       </c>
       <c r="E72">
-        <v>-17.5907370907049</v>
+        <v>-19.23305158822266</v>
       </c>
       <c r="F72">
-        <v>4.596682810797893</v>
+        <v>2.763782353269964</v>
       </c>
       <c r="G72">
-        <v>-10.11700183431677</v>
+        <v>-13.09603927492195</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-9.637498822623915</v>
       </c>
       <c r="E73">
-        <v>-17.53502780346254</v>
+        <v>-21.44555530499421</v>
       </c>
       <c r="F73">
-        <v>4.51358417770887</v>
+        <v>2.724788346220014</v>
       </c>
       <c r="G73">
-        <v>-9.627514502516748</v>
+        <v>-13.80560174253611</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-9.763907265005662</v>
       </c>
       <c r="E74">
-        <v>-17.28045963712135</v>
+        <v>-20.11382619729252</v>
       </c>
       <c r="F74">
-        <v>3.80746197230963</v>
+        <v>2.087037892602126</v>
       </c>
       <c r="G74">
-        <v>-9.948733425646692</v>
+        <v>-13.4834757299284</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-9.84795603869018</v>
       </c>
       <c r="E75">
-        <v>-17.89642720011868</v>
+        <v>-21.49942150331545</v>
       </c>
       <c r="F75">
-        <v>4.1360999542343</v>
+        <v>2.403060073204406</v>
       </c>
       <c r="G75">
-        <v>-9.110523158376463</v>
+        <v>-12.02258164163112</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-9.879484414909331</v>
       </c>
       <c r="E76">
-        <v>-16.33937028274332</v>
+        <v>-22.31415737593146</v>
       </c>
       <c r="F76">
-        <v>3.845151005685258</v>
+        <v>3.075865857260546</v>
       </c>
       <c r="G76">
-        <v>-9.717243528813153</v>
+        <v>-12.10208770330225</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-9.85566914119404</v>
       </c>
       <c r="E77">
-        <v>-17.52730675527946</v>
+        <v>-21.8565731913524</v>
       </c>
       <c r="F77">
-        <v>3.804582794955361</v>
+        <v>2.296080738616471</v>
       </c>
       <c r="G77">
-        <v>-9.475557151718661</v>
+        <v>-11.83304297787122</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-9.768907091634709</v>
       </c>
       <c r="E78">
-        <v>-18.48622018335167</v>
+        <v>-20.2974829891476</v>
       </c>
       <c r="F78">
-        <v>4.023797784064573</v>
+        <v>2.032944833354376</v>
       </c>
       <c r="G78">
-        <v>-9.064503264835054</v>
+        <v>-12.36157157321587</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-9.61903908598147</v>
       </c>
       <c r="E79">
-        <v>-18.51696399338975</v>
+        <v>-21.72116729004905</v>
       </c>
       <c r="F79">
-        <v>3.695424281027781</v>
+        <v>2.357867441201425</v>
       </c>
       <c r="G79">
-        <v>-8.814967584266949</v>
+        <v>-12.97013922806347</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-9.406522191428289</v>
       </c>
       <c r="E80">
-        <v>-20.11489038868433</v>
+        <v>-22.50868703387895</v>
       </c>
       <c r="F80">
-        <v>3.339796782892192</v>
+        <v>1.741110593198602</v>
       </c>
       <c r="G80">
-        <v>-8.63726743135549</v>
+        <v>-12.77755486240745</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-9.133891856871701</v>
       </c>
       <c r="E81">
-        <v>-19.55929191268325</v>
+        <v>-20.54387273143094</v>
       </c>
       <c r="F81">
-        <v>3.85231410754079</v>
+        <v>2.613189341476742</v>
       </c>
       <c r="G81">
-        <v>-8.76358791749746</v>
+        <v>-12.64825819582567</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-8.813125322693093</v>
       </c>
       <c r="E82">
-        <v>-18.4927276005007</v>
+        <v>-21.04843983383958</v>
       </c>
       <c r="F82">
-        <v>3.458383098134382</v>
+        <v>2.179003695111694</v>
       </c>
       <c r="G82">
-        <v>-7.818897263502112</v>
+        <v>-10.75507969210144</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-8.451947927005918</v>
       </c>
       <c r="E83">
-        <v>-19.90259099873073</v>
+        <v>-21.64641124113042</v>
       </c>
       <c r="F83">
-        <v>3.477789830422177</v>
+        <v>2.28719456472494</v>
       </c>
       <c r="G83">
-        <v>-8.799686106057672</v>
+        <v>-12.93546126353961</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-8.069330119628233</v>
       </c>
       <c r="E84">
-        <v>-21.6443281430869</v>
+        <v>-22.9686848951041</v>
       </c>
       <c r="F84">
-        <v>3.378830382590028</v>
+        <v>2.200502502913785</v>
       </c>
       <c r="G84">
-        <v>-8.284942622338553</v>
+        <v>-11.9588668821823</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-7.67989929904017</v>
       </c>
       <c r="E85">
-        <v>-21.38162230895392</v>
+        <v>-25.81998874081966</v>
       </c>
       <c r="F85">
-        <v>3.48017805894266</v>
+        <v>1.870722669024082</v>
       </c>
       <c r="G85">
-        <v>-8.417328027908468</v>
+        <v>-12.23431420268628</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-7.302963799577211</v>
       </c>
       <c r="E86">
-        <v>-23.8706754048999</v>
+        <v>-25.07686162768694</v>
       </c>
       <c r="F86">
-        <v>3.33333843016903</v>
+        <v>2.037395046976761</v>
       </c>
       <c r="G86">
-        <v>-8.23557907780248</v>
+        <v>-11.93137280147866</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-6.957211118988294</v>
       </c>
       <c r="E87">
-        <v>-23.12931439663017</v>
+        <v>-26.59644995112283</v>
       </c>
       <c r="F87">
-        <v>3.288063445458447</v>
+        <v>1.769593544087781</v>
       </c>
       <c r="G87">
-        <v>-7.792234129728822</v>
+        <v>-9.975240963779635</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-6.657444475599307</v>
       </c>
       <c r="E88">
-        <v>-24.90808087294706</v>
+        <v>-26.54960288751348</v>
       </c>
       <c r="F88">
-        <v>2.964874995588803</v>
+        <v>1.410448635114</v>
       </c>
       <c r="G88">
-        <v>-6.962320089580007</v>
+        <v>-11.18277569141096</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-6.421751286793421</v>
       </c>
       <c r="E89">
-        <v>-26.26749254225764</v>
+        <v>-30.19574675529234</v>
       </c>
       <c r="F89">
-        <v>3.313854096291378</v>
+        <v>1.604139035984075</v>
       </c>
       <c r="G89">
-        <v>-7.730303754325677</v>
+        <v>-9.400305141065488</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-6.256596205671441</v>
       </c>
       <c r="E90">
-        <v>-27.14023363843789</v>
+        <v>-29.11728840612864</v>
       </c>
       <c r="F90">
-        <v>3.076225358503351</v>
+        <v>1.461627675477341</v>
       </c>
       <c r="G90">
-        <v>-6.673127383996973</v>
+        <v>-9.719921760154424</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-6.172358182286287</v>
       </c>
       <c r="E91">
-        <v>-29.77959584364646</v>
+        <v>-31.20719274609053</v>
       </c>
       <c r="F91">
-        <v>2.806287436334443</v>
+        <v>1.720402054648316</v>
       </c>
       <c r="G91">
-        <v>-6.156755111872531</v>
+        <v>-10.71770363296306</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-6.167490794640901</v>
       </c>
       <c r="E92">
-        <v>-30.1835606317377</v>
+        <v>-33.74498807201807</v>
       </c>
       <c r="F92">
-        <v>2.753540527114817</v>
+        <v>1.241369024169854</v>
       </c>
       <c r="G92">
-        <v>-6.973042946581707</v>
+        <v>-10.26939948767158</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-6.241626694992758</v>
       </c>
       <c r="E93">
-        <v>-31.65806120371622</v>
+        <v>-33.44238638187752</v>
       </c>
       <c r="F93">
-        <v>2.694308342171466</v>
+        <v>0.7622964010435056</v>
       </c>
       <c r="G93">
-        <v>-6.906997563073246</v>
+        <v>-9.276864829542683</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-6.385868699617528</v>
       </c>
       <c r="E94">
-        <v>-33.64307023600144</v>
+        <v>-36.49386689262813</v>
       </c>
       <c r="F94">
-        <v>2.379491361770836</v>
+        <v>0.8922299691698197</v>
       </c>
       <c r="G94">
-        <v>-5.969735773268024</v>
+        <v>-9.589522681908072</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-6.589916957462073</v>
       </c>
       <c r="E95">
-        <v>-35.56233488264331</v>
+        <v>-35.89359049206738</v>
       </c>
       <c r="F95">
-        <v>2.181344412454714</v>
+        <v>1.543112512238532</v>
       </c>
       <c r="G95">
-        <v>-5.263801663564914</v>
+        <v>-10.85562427067464</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-6.847795287641548</v>
       </c>
       <c r="E96">
-        <v>-36.88940645482811</v>
+        <v>-39.26392765040908</v>
       </c>
       <c r="F96">
-        <v>1.99000106375132</v>
+        <v>0.2128747693003794</v>
       </c>
       <c r="G96">
-        <v>-5.916601517362721</v>
+        <v>-9.684588307613783</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-7.1415591395377</v>
       </c>
       <c r="E97">
-        <v>-38.2121035211215</v>
+        <v>-41.06226845562412</v>
       </c>
       <c r="F97">
-        <v>1.553650491399866</v>
+        <v>0.3254960562120671</v>
       </c>
       <c r="G97">
-        <v>-5.943966486790337</v>
+        <v>-8.783537264917108</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-7.476188428402377</v>
       </c>
       <c r="E98">
-        <v>-42.37823847377912</v>
+        <v>-40.81261141934425</v>
       </c>
       <c r="F98">
-        <v>1.62197631570967</v>
+        <v>-0.03610755619543334</v>
       </c>
       <c r="G98">
-        <v>-6.047364755618394</v>
+        <v>-9.182236195848155</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-7.827831868568889</v>
       </c>
       <c r="E99">
-        <v>-43.64869279968303</v>
+        <v>-45.43590261578721</v>
       </c>
       <c r="F99">
-        <v>1.290660287081991</v>
+        <v>0.6137495372930318</v>
       </c>
       <c r="G99">
-        <v>-5.484879894677444</v>
+        <v>-9.260719298947658</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-8.217305522226617</v>
       </c>
       <c r="E100">
-        <v>-45.62360333493114</v>
+        <v>-46.33132683827188</v>
       </c>
       <c r="F100">
-        <v>0.8436862154497697</v>
+        <v>-0.1317823979589612</v>
       </c>
       <c r="G100">
-        <v>-6.314221210447966</v>
+        <v>-8.254363113192305</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-8.60351929010988</v>
       </c>
       <c r="E101">
-        <v>-47.93957815430395</v>
+        <v>-47.89042156895069</v>
       </c>
       <c r="F101">
-        <v>0.6977287108710394</v>
+        <v>-0.4795174976649584</v>
       </c>
       <c r="G101">
-        <v>-5.573433677307409</v>
+        <v>-8.985775181365646</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-9.045509076628639</v>
       </c>
       <c r="E102">
-        <v>-49.83902280233274</v>
+        <v>-51.18529170795456</v>
       </c>
       <c r="F102">
-        <v>0.4178245273762715</v>
+        <v>-0.4949515036638736</v>
       </c>
       <c r="G102">
-        <v>-5.760515916277163</v>
+        <v>-9.642551000356118</v>
       </c>
     </row>
   </sheetData>
